--- a/education_forms/034_faculty_job_application_form--education_forms.xlsx
+++ b/education_forms/034_faculty_job_application_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'professor'}</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Professor'}</t>
+          <t>Professor</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'instructor'}</t>
+          <t>instructor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Instructor'}</t>
+          <t>Instructor</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'professor'}</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Professor'}</t>
+          <t>Professor</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'instructor'}</t>
+          <t>instructor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Instructor'}</t>
+          <t>Instructor</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'tenured'}</t>
+          <t>tenured</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Tenured'}</t>
+          <t>Tenured</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'non-tenured'}</t>
+          <t>non-tenured</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Tenured'}</t>
+          <t>Non-Tenured</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'tenure-track'}</t>
+          <t>tenure-track</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Tenure-Track'}</t>
+          <t>Tenure-Track</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'tenure-track_(non-tenurable)'}</t>
+          <t>tenure-track_(non-tenurable)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Tenure-Track (Non-tenurable)'}</t>
+          <t>Tenure-Track (Non-tenurable)</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'tenure-track_(non-tenurable)/tenured'}</t>
+          <t>tenure-track_(non-tenurable)/tenured</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Tenure-Track (Non-tenurable)/Tenured'}</t>
+          <t>Tenure-Track (Non-tenurable)/Tenured</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'tenure-track_(non-tenurable)/tenured'}</t>
+          <t>tenure-track_(non-tenurable)/tenured_(part-time)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Tenure-Track (Non-tenurable)/Tenured'}</t>
+          <t>Tenure-Track (Non-tenurable)/Tenured (part-time)</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'tenure-track_(non-tenurable)/tenured_(part-time)'}</t>
+          <t>tenure-track_(non-tenurable)/tenured_(part-time)/tenured</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Tenure-Track (Non-tenurable)/Tenured (part-time)'}</t>
+          <t>Tenure-Track (Non-tenurable)/Tenured (part-time)/Tenured</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'tenure-track_(non-tenurable)/tenured_(part-time)/tenured'}</t>
+          <t>tenure-track_(non-tenurable)/tenure-track_(non-tenurable)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Tenure-Track (Non-tenurable)/Tenured (part-time)/Tenured'}</t>
+          <t>Tenure-Track (Non-tenurable)/Tenure-Track (Non-tenurable)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_classification_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'tenure-track_(non-tenurable)/tenure-track_(non-tenurable)'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Tenure-Track (Non-tenurable)/Tenure-Track (Non-tenurable)'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>benefits_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>tenured</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Tenured</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'tenured'}</t>
+          <t>non-tenured</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Tenured'}</t>
+          <t>Non-Tenured</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'non-tenured'}</t>
+          <t>adjunct</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Tenured'}</t>
+          <t>Adjunct</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'adjunct'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Adjunct'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>employment_type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>tenured</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Tenured</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'tenured'}</t>
+          <t>tenured_(part-time)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Tenured'}</t>
+          <t>Tenured (Part-time)</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'tenured_(part-time)'}</t>
+          <t>non-tenured</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Tenured (Part-time)'}</t>
+          <t>Non-Tenured</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'non-tenured'}</t>
+          <t>non-tenured_(part-time)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Tenured'}</t>
+          <t>Non-Tenured (Part-time)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>employment_type_choices</t>
+          <t>job_location_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'non-tenured_(part-time)'}</t>
+          <t>new_brunswick</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Tenured (Part-time)'}</t>
+          <t>New Brunswick</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'new_brunswick'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'New Brunswick'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>ontario</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Ontario</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_location_choices</t>
+          <t>work_status_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'ontario'}</t>
+          <t>tenured</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Ontario'}</t>
+          <t>Tenured</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'tenured'}</t>
+          <t>non-tenured</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Tenured'}</t>
+          <t>Non-Tenured</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'non-tenured'}</t>
+          <t>adjunct</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Tenured'}</t>
+          <t>Adjunct</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'adjunct'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Adjunct'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>work_status_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
